--- a/results/eval_rl_games180.xlsx
+++ b/results/eval_rl_games180.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>time</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -469,7 +474,10 @@
         <v>2048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4920680522918701</v>
+        <v>0.6321899890899658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1127</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +494,10 @@
         <v>2048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8492119312286377</v>
+        <v>0.9215199947357178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1795</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +514,10 @@
         <v>4096</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2434401512146</v>
+        <v>1.253277540206909</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2397</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +534,10 @@
         <v>1024</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5584189891815186</v>
+        <v>0.4760715961456299</v>
+      </c>
+      <c r="F5" t="n">
+        <v>965</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +554,10 @@
         <v>2048</v>
       </c>
       <c r="E6" t="n">
-        <v>1.051078796386719</v>
+        <v>0.8122689723968506</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +574,10 @@
         <v>1024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6174213886260986</v>
+        <v>0.6126565933227539</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1084</v>
       </c>
     </row>
     <row r="8">
@@ -571,7 +594,10 @@
         <v>1024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.345862865447998</v>
+        <v>0.4456272125244141</v>
+      </c>
+      <c r="F8" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +614,10 @@
         <v>2048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8203170299530029</v>
+        <v>1.120033502578735</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1815</v>
       </c>
     </row>
     <row r="10">
@@ -605,7 +634,10 @@
         <v>2048</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9869437217712402</v>
+        <v>1.231918096542358</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2066</v>
       </c>
     </row>
     <row r="11">
@@ -622,7 +654,10 @@
         <v>1024</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4397194385528564</v>
+        <v>0.4285097122192383</v>
+      </c>
+      <c r="F11" t="n">
+        <v>828</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +674,10 @@
         <v>1024</v>
       </c>
       <c r="E12" t="n">
-        <v>0.386866569519043</v>
+        <v>0.5298919677734375</v>
+      </c>
+      <c r="F12" t="n">
+        <v>931</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +694,10 @@
         <v>2048</v>
       </c>
       <c r="E13" t="n">
-        <v>1.028847217559814</v>
+        <v>1.081247329711914</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1886</v>
       </c>
     </row>
     <row r="14">
@@ -673,7 +714,10 @@
         <v>1024</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5179393291473389</v>
+        <v>0.5549798011779785</v>
+      </c>
+      <c r="F14" t="n">
+        <v>928</v>
       </c>
     </row>
     <row r="15">
@@ -690,7 +734,10 @@
         <v>2048</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7450814247131348</v>
+        <v>0.7735199928283691</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1633</v>
       </c>
     </row>
     <row r="16">
@@ -707,7 +754,10 @@
         <v>1024</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4862072467803955</v>
+        <v>0.7025320529937744</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1095</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +774,10 @@
         <v>1024</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8379697799682617</v>
+        <v>0.8305990695953369</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1676</v>
       </c>
     </row>
     <row r="18">
@@ -741,7 +794,10 @@
         <v>1024</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3840100765228271</v>
+        <v>0.5866925716400146</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1037</v>
       </c>
     </row>
     <row r="19">
@@ -758,7 +814,10 @@
         <v>1024</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2678031921386719</v>
+        <v>0.3753008842468262</v>
+      </c>
+      <c r="F19" t="n">
+        <v>631</v>
       </c>
     </row>
     <row r="20">
@@ -775,7 +834,10 @@
         <v>1024</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7035367488861084</v>
+        <v>0.8127455711364746</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1397</v>
       </c>
     </row>
     <row r="21">
@@ -792,7 +854,10 @@
         <v>2048</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7580938339233398</v>
+        <v>0.7450492382049561</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1397</v>
       </c>
     </row>
     <row r="22">
@@ -809,7 +874,10 @@
         <v>2048</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8317646980285645</v>
+        <v>0.8322985172271729</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1675</v>
       </c>
     </row>
     <row r="23">
@@ -826,7 +894,10 @@
         <v>8192</v>
       </c>
       <c r="E23" t="n">
-        <v>2.269100427627563</v>
+        <v>2.450613260269165</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4709</v>
       </c>
     </row>
     <row r="24">
@@ -843,7 +914,10 @@
         <v>1024</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4894077777862549</v>
+        <v>0.5036807060241699</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="25">
@@ -860,7 +934,10 @@
         <v>2048</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7050879001617432</v>
+        <v>0.8130733966827393</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1587</v>
       </c>
     </row>
     <row r="26">
@@ -877,7 +954,10 @@
         <v>2048</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6157712936401367</v>
+        <v>0.659731388092041</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1229</v>
       </c>
     </row>
     <row r="27">
@@ -894,7 +974,10 @@
         <v>1024</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7148077487945557</v>
+        <v>0.7121624946594238</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1353</v>
       </c>
     </row>
     <row r="28">
@@ -911,7 +994,10 @@
         <v>2048</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6978030204772949</v>
+        <v>0.6984248161315918</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1609</v>
       </c>
     </row>
     <row r="29">
@@ -928,7 +1014,10 @@
         <v>1024</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3916254043579102</v>
+        <v>0.3977100849151611</v>
+      </c>
+      <c r="F29" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="30">
@@ -945,7 +1034,10 @@
         <v>2048</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8602774143218994</v>
+        <v>0.9596035480499268</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1728</v>
       </c>
     </row>
     <row r="31">
@@ -962,7 +1054,10 @@
         <v>2048</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6254174709320068</v>
+        <v>0.7492296695709229</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1243</v>
       </c>
     </row>
     <row r="32">
@@ -979,7 +1074,10 @@
         <v>2048</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6043496131896973</v>
+        <v>0.7349386215209961</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1321</v>
       </c>
     </row>
     <row r="33">
@@ -996,7 +1094,10 @@
         <v>1024</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4554944038391113</v>
+        <v>0.5602524280548096</v>
+      </c>
+      <c r="F33" t="n">
+        <v>902</v>
       </c>
     </row>
     <row r="34">
@@ -1013,7 +1114,10 @@
         <v>1024</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5326836109161377</v>
+        <v>0.5610535144805908</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="35">
@@ -1030,7 +1134,10 @@
         <v>4096</v>
       </c>
       <c r="E35" t="n">
-        <v>1.139178514480591</v>
+        <v>1.452642679214478</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2570</v>
       </c>
     </row>
     <row r="36">
@@ -1047,7 +1154,10 @@
         <v>2048</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9871137142181396</v>
+        <v>0.8460829257965088</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1768</v>
       </c>
     </row>
     <row r="37">
@@ -1064,7 +1174,10 @@
         <v>2048</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7109754085540771</v>
+        <v>0.7351129055023193</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1453</v>
       </c>
     </row>
     <row r="38">
@@ -1081,7 +1194,10 @@
         <v>1024</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3110361099243164</v>
+        <v>0.3619060516357422</v>
+      </c>
+      <c r="F38" t="n">
+        <v>647</v>
       </c>
     </row>
     <row r="39">
@@ -1098,7 +1214,10 @@
         <v>4096</v>
       </c>
       <c r="E39" t="n">
-        <v>1.089887857437134</v>
+        <v>1.121190547943115</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2244</v>
       </c>
     </row>
     <row r="40">
@@ -1115,7 +1234,10 @@
         <v>2048</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8439586162567139</v>
+        <v>0.9513731002807617</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1812</v>
       </c>
     </row>
     <row r="41">
@@ -1132,7 +1254,10 @@
         <v>1024</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5436086654663086</v>
+        <v>0.5905008316040039</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1057</v>
       </c>
     </row>
     <row r="42">
@@ -1149,7 +1274,10 @@
         <v>2048</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5209252834320068</v>
+        <v>0.5944805145263672</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1071</v>
       </c>
     </row>
     <row r="43">
@@ -1166,7 +1294,10 @@
         <v>2048</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5745007991790771</v>
+        <v>0.7565453052520752</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1260</v>
       </c>
     </row>
     <row r="44">
@@ -1183,7 +1314,10 @@
         <v>1024</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4791371822357178</v>
+        <v>0.5333817005157471</v>
+      </c>
+      <c r="F44" t="n">
+        <v>998</v>
       </c>
     </row>
     <row r="45">
@@ -1200,7 +1334,10 @@
         <v>512</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2955899238586426</v>
+        <v>0.3511462211608887</v>
+      </c>
+      <c r="F45" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="46">
@@ -1217,7 +1354,10 @@
         <v>1024</v>
       </c>
       <c r="E46" t="n">
-        <v>0.518944263458252</v>
+        <v>0.4136600494384766</v>
+      </c>
+      <c r="F46" t="n">
+        <v>916</v>
       </c>
     </row>
     <row r="47">
@@ -1234,7 +1374,10 @@
         <v>2048</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7444894313812256</v>
+        <v>1.075432062149048</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1684</v>
       </c>
     </row>
     <row r="48">
@@ -1251,7 +1394,10 @@
         <v>2048</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6586925983428955</v>
+        <v>0.7702839374542236</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1404</v>
       </c>
     </row>
     <row r="49">
@@ -1268,7 +1414,10 @@
         <v>1024</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4645147323608398</v>
+        <v>0.5115275382995605</v>
+      </c>
+      <c r="F49" t="n">
+        <v>906</v>
       </c>
     </row>
     <row r="50">
@@ -1285,7 +1434,10 @@
         <v>1024</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5510051250457764</v>
+        <v>0.5700736045837402</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1068</v>
       </c>
     </row>
     <row r="51">
@@ -1302,7 +1454,10 @@
         <v>2048</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8364109992980957</v>
+        <v>0.8766930103302002</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1525</v>
       </c>
     </row>
     <row r="52">
@@ -1319,7 +1474,10 @@
         <v>2048</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9162352085113525</v>
+        <v>0.9248123168945312</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1836</v>
       </c>
     </row>
     <row r="53">
@@ -1336,7 +1494,10 @@
         <v>2048</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6330819129943848</v>
+        <v>0.692669153213501</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1548</v>
       </c>
     </row>
     <row r="54">
@@ -1353,7 +1514,10 @@
         <v>1024</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4489693641662598</v>
+        <v>0.6940047740936279</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1167</v>
       </c>
     </row>
     <row r="55">
@@ -1370,7 +1534,10 @@
         <v>1024</v>
       </c>
       <c r="E55" t="n">
-        <v>0.465569019317627</v>
+        <v>0.63364577293396</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1311</v>
       </c>
     </row>
     <row r="56">
@@ -1387,7 +1554,10 @@
         <v>4096</v>
       </c>
       <c r="E56" t="n">
-        <v>1.092777967453003</v>
+        <v>1.185395002365112</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2579</v>
       </c>
     </row>
     <row r="57">
@@ -1404,7 +1574,10 @@
         <v>1024</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4692471027374268</v>
+        <v>0.3908822536468506</v>
+      </c>
+      <c r="F57" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="58">
@@ -1421,7 +1594,10 @@
         <v>2048</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8213915824890137</v>
+        <v>1.061150789260864</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1908</v>
       </c>
     </row>
     <row r="59">
@@ -1438,7 +1614,10 @@
         <v>2048</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8597383499145508</v>
+        <v>1.086068153381348</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1998</v>
       </c>
     </row>
     <row r="60">
@@ -1455,7 +1634,10 @@
         <v>2048</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7963814735412598</v>
+        <v>0.8642549514770508</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="61">
@@ -1472,7 +1654,10 @@
         <v>1024</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5550403594970703</v>
+        <v>0.5686547756195068</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1182</v>
       </c>
     </row>
     <row r="62">
@@ -1489,7 +1674,10 @@
         <v>2048</v>
       </c>
       <c r="E62" t="n">
-        <v>1.185386180877686</v>
+        <v>1.226170301437378</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2117</v>
       </c>
     </row>
     <row r="63">
@@ -1506,7 +1694,10 @@
         <v>512</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2796823978424072</v>
+        <v>0.3022224903106689</v>
+      </c>
+      <c r="F63" t="n">
+        <v>635</v>
       </c>
     </row>
     <row r="64">
@@ -1523,7 +1714,10 @@
         <v>2048</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6539864540100098</v>
+        <v>0.953465461730957</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1589</v>
       </c>
     </row>
     <row r="65">
@@ -1540,7 +1734,10 @@
         <v>2048</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8741836547851562</v>
+        <v>1.184501886367798</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1943</v>
       </c>
     </row>
     <row r="66">
@@ -1557,7 +1754,10 @@
         <v>2048</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8461868762969971</v>
+        <v>0.9289023876190186</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="67">
@@ -1574,7 +1774,10 @@
         <v>1024</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5707511901855469</v>
+        <v>0.4941179752349854</v>
+      </c>
+      <c r="F67" t="n">
+        <v>964</v>
       </c>
     </row>
     <row r="68">
@@ -1591,7 +1794,10 @@
         <v>1024</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4981048107147217</v>
+        <v>0.5304994583129883</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1022</v>
       </c>
     </row>
     <row r="69">
@@ -1608,7 +1814,10 @@
         <v>2048</v>
       </c>
       <c r="E69" t="n">
-        <v>0.80460524559021</v>
+        <v>0.7587759494781494</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1536</v>
       </c>
     </row>
     <row r="70">
@@ -1625,7 +1834,10 @@
         <v>2048</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5739185810089111</v>
+        <v>0.6085319519042969</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1349</v>
       </c>
     </row>
     <row r="71">
@@ -1642,7 +1854,10 @@
         <v>1024</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3630557060241699</v>
+        <v>0.3944847583770752</v>
+      </c>
+      <c r="F71" t="n">
+        <v>684</v>
       </c>
     </row>
     <row r="72">
@@ -1659,7 +1874,10 @@
         <v>2048</v>
       </c>
       <c r="E72" t="n">
-        <v>1.020023584365845</v>
+        <v>0.9921939373016357</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1938</v>
       </c>
     </row>
     <row r="73">
@@ -1676,7 +1894,10 @@
         <v>2048</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7865266799926758</v>
+        <v>0.8242392539978027</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1704</v>
       </c>
     </row>
     <row r="74">
@@ -1693,7 +1914,10 @@
         <v>4096</v>
       </c>
       <c r="E74" t="n">
-        <v>1.459169864654541</v>
+        <v>1.510574579238892</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2719</v>
       </c>
     </row>
     <row r="75">
@@ -1710,7 +1934,10 @@
         <v>1024</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5014419555664062</v>
+        <v>0.5375542640686035</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1114</v>
       </c>
     </row>
     <row r="76">
@@ -1727,7 +1954,10 @@
         <v>1024</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4029028415679932</v>
+        <v>0.4666142463684082</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1002</v>
       </c>
     </row>
     <row r="77">
@@ -1744,7 +1974,10 @@
         <v>2048</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8047018051147461</v>
+        <v>0.9721202850341797</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1921</v>
       </c>
     </row>
     <row r="78">
@@ -1761,7 +1994,10 @@
         <v>1024</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4504139423370361</v>
+        <v>0.3678767681121826</v>
+      </c>
+      <c r="F78" t="n">
+        <v>818</v>
       </c>
     </row>
     <row r="79">
@@ -1778,7 +2014,10 @@
         <v>1024</v>
       </c>
       <c r="E79" t="n">
-        <v>0.544952392578125</v>
+        <v>0.5234060287475586</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1237</v>
       </c>
     </row>
     <row r="80">
@@ -1795,7 +2034,10 @@
         <v>1024</v>
       </c>
       <c r="E80" t="n">
-        <v>0.6856012344360352</v>
+        <v>0.5998015403747559</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1248</v>
       </c>
     </row>
     <row r="81">
@@ -1812,7 +2054,10 @@
         <v>2048</v>
       </c>
       <c r="E81" t="n">
-        <v>0.642441987991333</v>
+        <v>0.7637495994567871</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1286</v>
       </c>
     </row>
     <row r="82">
@@ -1829,7 +2074,10 @@
         <v>2048</v>
       </c>
       <c r="E82" t="n">
-        <v>0.734018087387085</v>
+        <v>0.7533469200134277</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1622</v>
       </c>
     </row>
     <row r="83">
@@ -1846,7 +2094,10 @@
         <v>2048</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8760085105895996</v>
+        <v>0.8760101795196533</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1766</v>
       </c>
     </row>
     <row r="84">
@@ -1863,7 +2114,10 @@
         <v>512</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2496001720428467</v>
+        <v>0.263890266418457</v>
+      </c>
+      <c r="F84" t="n">
+        <v>468</v>
       </c>
     </row>
     <row r="85">
@@ -1880,7 +2134,10 @@
         <v>2048</v>
       </c>
       <c r="E85" t="n">
-        <v>0.6348016262054443</v>
+        <v>0.5287129878997803</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1188</v>
       </c>
     </row>
     <row r="86">
@@ -1897,7 +2154,10 @@
         <v>512</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2303245067596436</v>
+        <v>0.2250919342041016</v>
+      </c>
+      <c r="F86" t="n">
+        <v>557</v>
       </c>
     </row>
     <row r="87">
@@ -1914,7 +2174,10 @@
         <v>2048</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6032826900482178</v>
+        <v>0.6535990238189697</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1310</v>
       </c>
     </row>
     <row r="88">
@@ -1931,7 +2194,10 @@
         <v>2048</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6572954654693604</v>
+        <v>0.6861112117767334</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1431</v>
       </c>
     </row>
     <row r="89">
@@ -1948,7 +2214,10 @@
         <v>2048</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5376200675964355</v>
+        <v>0.7407546043395996</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1379</v>
       </c>
     </row>
     <row r="90">
@@ -1965,7 +2234,10 @@
         <v>2048</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5606222152709961</v>
+        <v>0.655935525894165</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1283</v>
       </c>
     </row>
     <row r="91">
@@ -1982,7 +2254,10 @@
         <v>2048</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8565411567687988</v>
+        <v>0.9852442741394043</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1865</v>
       </c>
     </row>
     <row r="92">
@@ -1999,7 +2274,10 @@
         <v>2048</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7870414257049561</v>
+        <v>0.713590145111084</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1577</v>
       </c>
     </row>
     <row r="93">
@@ -2016,7 +2294,10 @@
         <v>1024</v>
       </c>
       <c r="E93" t="n">
-        <v>0.469404935836792</v>
+        <v>0.4867620468139648</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1013</v>
       </c>
     </row>
     <row r="94">
@@ -2033,7 +2314,10 @@
         <v>2048</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8044569492340088</v>
+        <v>0.7336471080780029</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1541</v>
       </c>
     </row>
     <row r="95">
@@ -2050,7 +2334,10 @@
         <v>1024</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3969919681549072</v>
+        <v>0.5355589389801025</v>
+      </c>
+      <c r="F95" t="n">
+        <v>979</v>
       </c>
     </row>
     <row r="96">
@@ -2067,7 +2354,10 @@
         <v>2048</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7480380535125732</v>
+        <v>0.8286697864532471</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1467</v>
       </c>
     </row>
     <row r="97">
@@ -2084,7 +2374,10 @@
         <v>1024</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4096357822418213</v>
+        <v>0.5643172264099121</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1011</v>
       </c>
     </row>
     <row r="98">
@@ -2101,7 +2394,10 @@
         <v>1024</v>
       </c>
       <c r="E98" t="n">
-        <v>0.5631251335144043</v>
+        <v>0.5947713851928711</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1092</v>
       </c>
     </row>
     <row r="99">
@@ -2118,7 +2414,10 @@
         <v>1024</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6191980838775635</v>
+        <v>0.6192357540130615</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1383</v>
       </c>
     </row>
     <row r="100">
@@ -2135,7 +2434,10 @@
         <v>1024</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5370838642120361</v>
+        <v>0.5038118362426758</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="101">
@@ -2152,7 +2454,10 @@
         <v>2048</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6716935634613037</v>
+        <v>0.9419450759887695</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1812</v>
       </c>
     </row>
     <row r="102">
@@ -2169,7 +2474,10 @@
         <v>1024</v>
       </c>
       <c r="E102" t="n">
-        <v>0.429344654083252</v>
+        <v>0.5109279155731201</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1070</v>
       </c>
     </row>
     <row r="103">
@@ -2186,7 +2494,10 @@
         <v>2048</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8941764831542969</v>
+        <v>0.9168863296508789</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1759</v>
       </c>
     </row>
     <row r="104">
@@ -2203,7 +2514,10 @@
         <v>1024</v>
       </c>
       <c r="E104" t="n">
-        <v>0.5835094451904297</v>
+        <v>0.6106195449829102</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1173</v>
       </c>
     </row>
     <row r="105">
@@ -2220,7 +2534,10 @@
         <v>1024</v>
       </c>
       <c r="E105" t="n">
-        <v>0.631788969039917</v>
+        <v>0.7027502059936523</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1254</v>
       </c>
     </row>
     <row r="106">
@@ -2237,7 +2554,10 @@
         <v>2048</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7626824378967285</v>
+        <v>0.9284713268280029</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1719</v>
       </c>
     </row>
     <row r="107">
@@ -2254,7 +2574,10 @@
         <v>2048</v>
       </c>
       <c r="E107" t="n">
-        <v>0.681018590927124</v>
+        <v>0.957538366317749</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1728</v>
       </c>
     </row>
     <row r="108">
@@ -2271,7 +2594,10 @@
         <v>4096</v>
       </c>
       <c r="E108" t="n">
-        <v>1.633666753768921</v>
+        <v>1.94143271446228</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3649</v>
       </c>
     </row>
     <row r="109">
@@ -2288,7 +2614,10 @@
         <v>512</v>
       </c>
       <c r="E109" t="n">
-        <v>0.2449588775634766</v>
+        <v>0.2450110912322998</v>
+      </c>
+      <c r="F109" t="n">
+        <v>515</v>
       </c>
     </row>
     <row r="110">
@@ -2305,7 +2634,10 @@
         <v>4096</v>
       </c>
       <c r="E110" t="n">
-        <v>1.134955883026123</v>
+        <v>1.118603706359863</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2476</v>
       </c>
     </row>
     <row r="111">
@@ -2322,7 +2654,10 @@
         <v>1024</v>
       </c>
       <c r="E111" t="n">
-        <v>0.415546178817749</v>
+        <v>0.484997034072876</v>
+      </c>
+      <c r="F111" t="n">
+        <v>867</v>
       </c>
     </row>
     <row r="112">
@@ -2339,7 +2674,10 @@
         <v>2048</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9240686893463135</v>
+        <v>1.055877685546875</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1946</v>
       </c>
     </row>
     <row r="113">
@@ -2356,7 +2694,10 @@
         <v>1024</v>
       </c>
       <c r="E113" t="n">
-        <v>0.6395270824432373</v>
+        <v>0.580596923828125</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1224</v>
       </c>
     </row>
     <row r="114">
@@ -2373,7 +2714,10 @@
         <v>4096</v>
       </c>
       <c r="E114" t="n">
-        <v>1.140589952468872</v>
+        <v>1.280756950378418</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2417</v>
       </c>
     </row>
     <row r="115">
@@ -2390,7 +2734,10 @@
         <v>2048</v>
       </c>
       <c r="E115" t="n">
-        <v>0.6253206729888916</v>
+        <v>0.8880770206451416</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1416</v>
       </c>
     </row>
     <row r="116">
@@ -2407,7 +2754,10 @@
         <v>2048</v>
       </c>
       <c r="E116" t="n">
-        <v>0.852031946182251</v>
+        <v>0.8966617584228516</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1548</v>
       </c>
     </row>
     <row r="117">
@@ -2424,7 +2774,10 @@
         <v>4096</v>
       </c>
       <c r="E117" t="n">
-        <v>1.356570720672607</v>
+        <v>1.552976846694946</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2631</v>
       </c>
     </row>
     <row r="118">
@@ -2441,7 +2794,10 @@
         <v>1024</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6660807132720947</v>
+        <v>0.7361636161804199</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1288</v>
       </c>
     </row>
     <row r="119">
@@ -2458,7 +2814,10 @@
         <v>2048</v>
       </c>
       <c r="E119" t="n">
-        <v>0.8614199161529541</v>
+        <v>1.093281507492065</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2028</v>
       </c>
     </row>
     <row r="120">
@@ -2475,7 +2834,10 @@
         <v>4096</v>
       </c>
       <c r="E120" t="n">
-        <v>0.87839674949646</v>
+        <v>1.153573989868164</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2090</v>
       </c>
     </row>
     <row r="121">
@@ -2492,7 +2854,10 @@
         <v>2048</v>
       </c>
       <c r="E121" t="n">
-        <v>0.6259787082672119</v>
+        <v>0.5824534893035889</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1213</v>
       </c>
     </row>
     <row r="122">
@@ -2509,7 +2874,10 @@
         <v>2048</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5388340950012207</v>
+        <v>0.6328158378601074</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1324</v>
       </c>
     </row>
     <row r="123">
@@ -2526,7 +2894,10 @@
         <v>1024</v>
       </c>
       <c r="E123" t="n">
-        <v>0.4958064556121826</v>
+        <v>0.5429782867431641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="124">
@@ -2543,7 +2914,10 @@
         <v>4096</v>
       </c>
       <c r="E124" t="n">
-        <v>1.616287231445312</v>
+        <v>1.685557126998901</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3297</v>
       </c>
     </row>
     <row r="125">
@@ -2560,7 +2934,10 @@
         <v>1024</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3291475772857666</v>
+        <v>0.4606964588165283</v>
+      </c>
+      <c r="F125" t="n">
+        <v>778</v>
       </c>
     </row>
     <row r="126">
@@ -2577,7 +2954,10 @@
         <v>4096</v>
       </c>
       <c r="E126" t="n">
-        <v>1.291678667068481</v>
+        <v>1.609594583511353</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2678</v>
       </c>
     </row>
     <row r="127">
@@ -2594,7 +2974,10 @@
         <v>256</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1268463134765625</v>
+        <v>0.1375901699066162</v>
+      </c>
+      <c r="F127" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="128">
@@ -2611,7 +2994,10 @@
         <v>1024</v>
       </c>
       <c r="E128" t="n">
-        <v>0.5532279014587402</v>
+        <v>0.5341165065765381</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="129">
@@ -2628,7 +3014,10 @@
         <v>2048</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7702677249908447</v>
+        <v>0.7359678745269775</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1375</v>
       </c>
     </row>
     <row r="130">
@@ -2645,7 +3034,10 @@
         <v>4096</v>
       </c>
       <c r="E130" t="n">
-        <v>1.020700454711914</v>
+        <v>1.209839820861816</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2270</v>
       </c>
     </row>
     <row r="131">
@@ -2662,7 +3054,10 @@
         <v>2048</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7793912887573242</v>
+        <v>0.9705691337585449</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1663</v>
       </c>
     </row>
     <row r="132">
@@ -2679,7 +3074,10 @@
         <v>4096</v>
       </c>
       <c r="E132" t="n">
-        <v>1.257143974304199</v>
+        <v>1.50185489654541</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2636</v>
       </c>
     </row>
     <row r="133">
@@ -2696,7 +3094,10 @@
         <v>2048</v>
       </c>
       <c r="E133" t="n">
-        <v>0.9642038345336914</v>
+        <v>1.062219619750977</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2079</v>
       </c>
     </row>
     <row r="134">
@@ -2713,7 +3114,10 @@
         <v>1024</v>
       </c>
       <c r="E134" t="n">
-        <v>0.532578706741333</v>
+        <v>0.5493161678314209</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1128</v>
       </c>
     </row>
     <row r="135">
@@ -2730,7 +3134,10 @@
         <v>1024</v>
       </c>
       <c r="E135" t="n">
-        <v>0.5713863372802734</v>
+        <v>0.6542198657989502</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1229</v>
       </c>
     </row>
     <row r="136">
@@ -2747,7 +3154,10 @@
         <v>2048</v>
       </c>
       <c r="E136" t="n">
-        <v>0.7199416160583496</v>
+        <v>0.9044113159179688</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1476</v>
       </c>
     </row>
     <row r="137">
@@ -2764,7 +3174,10 @@
         <v>1024</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3883771896362305</v>
+        <v>0.4664075374603271</v>
+      </c>
+      <c r="F137" t="n">
+        <v>939</v>
       </c>
     </row>
     <row r="138">
@@ -2781,7 +3194,10 @@
         <v>2048</v>
       </c>
       <c r="E138" t="n">
-        <v>0.7839438915252686</v>
+        <v>0.946183443069458</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1791</v>
       </c>
     </row>
     <row r="139">
@@ -2798,7 +3214,10 @@
         <v>4096</v>
       </c>
       <c r="E139" t="n">
-        <v>1.029107809066772</v>
+        <v>1.02763295173645</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2063</v>
       </c>
     </row>
     <row r="140">
@@ -2815,7 +3234,10 @@
         <v>2048</v>
       </c>
       <c r="E140" t="n">
-        <v>0.894197940826416</v>
+        <v>1.069112539291382</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1923</v>
       </c>
     </row>
     <row r="141">
@@ -2832,7 +3254,10 @@
         <v>8192</v>
       </c>
       <c r="E141" t="n">
-        <v>1.794481992721558</v>
+        <v>2.040994167327881</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4117</v>
       </c>
     </row>
     <row r="142">
@@ -2849,7 +3274,10 @@
         <v>1024</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4389331340789795</v>
+        <v>0.6254467964172363</v>
+      </c>
+      <c r="F142" t="n">
+        <v>949</v>
       </c>
     </row>
     <row r="143">
@@ -2866,7 +3294,10 @@
         <v>2048</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6108450889587402</v>
+        <v>0.656113862991333</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="144">
@@ -2883,7 +3314,10 @@
         <v>1024</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4648749828338623</v>
+        <v>0.5183343887329102</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="145">
@@ -2900,7 +3334,10 @@
         <v>1024</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5837564468383789</v>
+        <v>0.5073859691619873</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1212</v>
       </c>
     </row>
     <row r="146">
@@ -2917,7 +3354,10 @@
         <v>2048</v>
       </c>
       <c r="E146" t="n">
-        <v>0.6622259616851807</v>
+        <v>0.7625353336334229</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1323</v>
       </c>
     </row>
     <row r="147">
@@ -2934,7 +3374,10 @@
         <v>1024</v>
       </c>
       <c r="E147" t="n">
-        <v>0.6110820770263672</v>
+        <v>0.7384912967681885</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="148">
@@ -2951,7 +3394,10 @@
         <v>1024</v>
       </c>
       <c r="E148" t="n">
-        <v>0.4626364707946777</v>
+        <v>0.6853988170623779</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1228</v>
       </c>
     </row>
     <row r="149">
@@ -2968,7 +3414,10 @@
         <v>2048</v>
       </c>
       <c r="E149" t="n">
-        <v>0.8498048782348633</v>
+        <v>1.063281059265137</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1752</v>
       </c>
     </row>
     <row r="150">
@@ -2985,7 +3434,10 @@
         <v>1024</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3319671154022217</v>
+        <v>0.3705728054046631</v>
+      </c>
+      <c r="F150" t="n">
+        <v>769</v>
       </c>
     </row>
     <row r="151">
@@ -3002,7 +3454,10 @@
         <v>2048</v>
       </c>
       <c r="E151" t="n">
-        <v>0.735527515411377</v>
+        <v>0.8489353656768799</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1583</v>
       </c>
     </row>
     <row r="152">
@@ -3019,7 +3474,10 @@
         <v>1024</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3060557842254639</v>
+        <v>0.4843695163726807</v>
+      </c>
+      <c r="F152" t="n">
+        <v>732</v>
       </c>
     </row>
     <row r="153">
@@ -3036,7 +3494,10 @@
         <v>256</v>
       </c>
       <c r="E153" t="n">
-        <v>0.1692461967468262</v>
+        <v>0.1715600490570068</v>
+      </c>
+      <c r="F153" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="154">
@@ -3053,7 +3514,10 @@
         <v>2048</v>
       </c>
       <c r="E154" t="n">
-        <v>0.8581538200378418</v>
+        <v>0.8877658843994141</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1712</v>
       </c>
     </row>
     <row r="155">
@@ -3070,7 +3534,10 @@
         <v>2048</v>
       </c>
       <c r="E155" t="n">
-        <v>0.8325741291046143</v>
+        <v>0.9065673351287842</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1827</v>
       </c>
     </row>
     <row r="156">
@@ -3087,7 +3554,10 @@
         <v>4096</v>
       </c>
       <c r="E156" t="n">
-        <v>1.145459413528442</v>
+        <v>1.20514178276062</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2293</v>
       </c>
     </row>
     <row r="157">
@@ -3104,7 +3574,10 @@
         <v>2048</v>
       </c>
       <c r="E157" t="n">
-        <v>1.17455267906189</v>
+        <v>1.190483331680298</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2379</v>
       </c>
     </row>
     <row r="158">
@@ -3121,7 +3594,10 @@
         <v>2048</v>
       </c>
       <c r="E158" t="n">
-        <v>0.469228982925415</v>
+        <v>0.5346741676330566</v>
+      </c>
+      <c r="F158" t="n">
+        <v>959</v>
       </c>
     </row>
     <row r="159">
@@ -3138,7 +3614,10 @@
         <v>1024</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5487813949584961</v>
+        <v>0.5601739883422852</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1116</v>
       </c>
     </row>
     <row r="160">
@@ -3155,7 +3634,10 @@
         <v>2048</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7738046646118164</v>
+        <v>1.033343553543091</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1904</v>
       </c>
     </row>
     <row r="161">
@@ -3172,7 +3654,10 @@
         <v>2048</v>
       </c>
       <c r="E161" t="n">
-        <v>1.044395923614502</v>
+        <v>1.308841705322266</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2187</v>
       </c>
     </row>
     <row r="162">
@@ -3189,7 +3674,10 @@
         <v>4096</v>
       </c>
       <c r="E162" t="n">
-        <v>1.163615942001343</v>
+        <v>1.143629550933838</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2233</v>
       </c>
     </row>
     <row r="163">
@@ -3206,7 +3694,10 @@
         <v>2048</v>
       </c>
       <c r="E163" t="n">
-        <v>0.7956390380859375</v>
+        <v>0.810859203338623</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1562</v>
       </c>
     </row>
     <row r="164">
@@ -3223,7 +3714,10 @@
         <v>2048</v>
       </c>
       <c r="E164" t="n">
-        <v>0.6524350643157959</v>
+        <v>0.7245714664459229</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1422</v>
       </c>
     </row>
     <row r="165">
@@ -3240,7 +3734,10 @@
         <v>4096</v>
       </c>
       <c r="E165" t="n">
-        <v>1.403989315032959</v>
+        <v>1.449177503585815</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2870</v>
       </c>
     </row>
     <row r="166">
@@ -3257,7 +3754,10 @@
         <v>2048</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6191015243530273</v>
+        <v>0.5686664581298828</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1148</v>
       </c>
     </row>
     <row r="167">
@@ -3274,7 +3774,10 @@
         <v>2048</v>
       </c>
       <c r="E167" t="n">
-        <v>0.6405248641967773</v>
+        <v>0.6433055400848389</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1351</v>
       </c>
     </row>
     <row r="168">
@@ -3291,7 +3794,10 @@
         <v>2048</v>
       </c>
       <c r="E168" t="n">
-        <v>0.6538786888122559</v>
+        <v>0.7143485546112061</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1323</v>
       </c>
     </row>
     <row r="169">
@@ -3308,7 +3814,10 @@
         <v>2048</v>
       </c>
       <c r="E169" t="n">
-        <v>0.7038123607635498</v>
+        <v>0.9153461456298828</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1731</v>
       </c>
     </row>
     <row r="170">
@@ -3325,7 +3834,10 @@
         <v>1024</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3891968727111816</v>
+        <v>0.489687442779541</v>
+      </c>
+      <c r="F170" t="n">
+        <v>948</v>
       </c>
     </row>
     <row r="171">
@@ -3342,7 +3854,10 @@
         <v>2048</v>
       </c>
       <c r="E171" t="n">
-        <v>1.072409868240356</v>
+        <v>0.9537153244018555</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1941</v>
       </c>
     </row>
     <row r="172">
@@ -3359,7 +3874,10 @@
         <v>2048</v>
       </c>
       <c r="E172" t="n">
-        <v>0.6554126739501953</v>
+        <v>0.6181528568267822</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1334</v>
       </c>
     </row>
     <row r="173">
@@ -3376,7 +3894,10 @@
         <v>512</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3775637149810791</v>
+        <v>0.3783557415008545</v>
+      </c>
+      <c r="F173" t="n">
+        <v>738</v>
       </c>
     </row>
     <row r="174">
@@ -3393,7 +3914,10 @@
         <v>4096</v>
       </c>
       <c r="E174" t="n">
-        <v>1.385633230209351</v>
+        <v>1.558073759078979</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2973</v>
       </c>
     </row>
     <row r="175">
@@ -3410,7 +3934,10 @@
         <v>1024</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5408265590667725</v>
+        <v>0.599567174911499</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1085</v>
       </c>
     </row>
     <row r="176">
@@ -3427,7 +3954,10 @@
         <v>1024</v>
       </c>
       <c r="E176" t="n">
-        <v>0.5113749504089355</v>
+        <v>0.4111392498016357</v>
+      </c>
+      <c r="F176" t="n">
+        <v>878</v>
       </c>
     </row>
     <row r="177">
@@ -3444,7 +3974,10 @@
         <v>4096</v>
       </c>
       <c r="E177" t="n">
-        <v>0.7563240528106689</v>
+        <v>1.172668695449829</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1862</v>
       </c>
     </row>
     <row r="178">
@@ -3461,7 +3994,10 @@
         <v>1024</v>
       </c>
       <c r="E178" t="n">
-        <v>0.4279966354370117</v>
+        <v>0.5339834690093994</v>
+      </c>
+      <c r="F178" t="n">
+        <v>987</v>
       </c>
     </row>
     <row r="179">
@@ -3478,7 +4014,10 @@
         <v>1024</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4027431011199951</v>
+        <v>0.4850897789001465</v>
+      </c>
+      <c r="F179" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="180">
@@ -3495,7 +4034,10 @@
         <v>1024</v>
       </c>
       <c r="E180" t="n">
-        <v>0.5094010829925537</v>
+        <v>0.5251555442810059</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="181">
@@ -3512,7 +4054,10 @@
         <v>1024</v>
       </c>
       <c r="E181" t="n">
-        <v>0.3266010284423828</v>
+        <v>0.4263389110565186</v>
+      </c>
+      <c r="F181" t="n">
+        <v>681</v>
       </c>
     </row>
   </sheetData>
